--- a/Assets/Data/SE.xlsx
+++ b/Assets/Data/SE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>Id</t>
   </si>
@@ -34,115 +34,76 @@
     <t>DECIDE</t>
   </si>
   <si>
-    <t>decide7</t>
+    <t>cursor33</t>
   </si>
   <si>
     <t>CANCEL</t>
   </si>
   <si>
+    <t>cursor27</t>
+  </si>
+  <si>
     <t>CURSOR</t>
   </si>
   <si>
-    <t>cursor_move8</t>
+    <t>cursor11</t>
   </si>
   <si>
     <t>DAMAGE</t>
   </si>
   <si>
-    <t>damage</t>
+    <t>cursor32</t>
   </si>
   <si>
     <t>DEFEAT</t>
   </si>
   <si>
-    <t>defeat</t>
-  </si>
-  <si>
     <t>DEMIGOD</t>
   </si>
   <si>
-    <t>swordspecial</t>
-  </si>
-  <si>
     <t>DENY</t>
   </si>
   <si>
-    <t>beap3</t>
+    <t>Shot2</t>
   </si>
   <si>
     <t>LEVELUP</t>
   </si>
   <si>
-    <t>decide43</t>
-  </si>
-  <si>
     <t>CRITICAL</t>
   </si>
   <si>
-    <t>Sword2</t>
-  </si>
-  <si>
     <t>SKILL</t>
   </si>
   <si>
-    <t>Skill1</t>
-  </si>
-  <si>
     <t>AWAKEN</t>
   </si>
   <si>
-    <t>demigod</t>
-  </si>
-  <si>
     <t>COUNTUP</t>
   </si>
   <si>
-    <t>messagedisplay1</t>
-  </si>
-  <si>
     <t>MISS</t>
   </si>
   <si>
-    <t>Miss</t>
-  </si>
-  <si>
     <t>HEAL</t>
   </si>
   <si>
-    <t>Up1</t>
-  </si>
-  <si>
     <t>BUFF</t>
   </si>
   <si>
-    <t>Sword1</t>
-  </si>
-  <si>
     <t>DEBUFF</t>
   </si>
   <si>
-    <t>power36</t>
-  </si>
-  <si>
     <t>BATTLESTART</t>
   </si>
   <si>
     <t>LEARNSKILL</t>
   </si>
   <si>
-    <t>Flash2</t>
-  </si>
-  <si>
     <t>CURSOR_MOVE</t>
   </si>
   <si>
-    <t>cursor</t>
-  </si>
-  <si>
     <t>PLAYSTART</t>
-  </si>
-  <si>
-    <t>gamestart</t>
   </si>
 </sst>
 </file>
@@ -150,10 +111,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -164,14 +125,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -186,68 +139,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -262,7 +155,52 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -276,6 +214,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -302,7 +263,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,187 +278,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -513,10 +474,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -533,6 +492,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -555,26 +525,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -594,17 +561,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -616,145 +577,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1113,8 +1074,7 @@
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="2" max="3" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1159,7 +1119,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1173,10 +1133,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1190,10 +1150,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5">
         <v>0.5</v>
@@ -1207,10 +1167,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
         <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
       </c>
       <c r="D6">
         <v>0.8</v>
@@ -1227,7 +1187,7 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D7">
         <v>0.8</v>
@@ -1241,10 +1201,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
         <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1258,10 +1218,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1275,10 +1235,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D10">
         <v>0.8</v>
@@ -1292,10 +1252,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D11">
         <v>0.6</v>
@@ -1309,10 +1269,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D12">
         <v>0.8</v>
@@ -1326,10 +1286,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1343,10 +1303,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D14">
         <v>0.6</v>
@@ -1360,10 +1320,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="D15">
         <v>0.8</v>
@@ -1377,10 +1337,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="D16">
         <v>0.8</v>
@@ -1394,10 +1354,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="D17">
         <v>0.8</v>
@@ -1411,10 +1371,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D18">
         <v>0.8</v>
@@ -1428,10 +1388,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="D19">
         <v>0.8</v>
@@ -1445,10 +1405,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D20">
         <v>0.8</v>
@@ -1462,10 +1422,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="D21">
         <v>0.8</v>

--- a/Assets/Data/SE.xlsx
+++ b/Assets/Data/SE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
   <si>
     <t>Id</t>
   </si>
@@ -52,15 +52,21 @@
     <t>DAMAGE</t>
   </si>
   <si>
+    <t>Damage4</t>
+  </si>
+  <si>
+    <t>DEFEAT</t>
+  </si>
+  <si>
+    <t>Collapse1</t>
+  </si>
+  <si>
+    <t>DEMIGOD</t>
+  </si>
+  <si>
     <t>cursor32</t>
   </si>
   <si>
-    <t>DEFEAT</t>
-  </si>
-  <si>
-    <t>DEMIGOD</t>
-  </si>
-  <si>
     <t>DENY</t>
   </si>
   <si>
@@ -95,6 +101,9 @@
   </si>
   <si>
     <t>BATTLESTART</t>
+  </si>
+  <si>
+    <t>Battle3</t>
   </si>
   <si>
     <t>LEARNSKILL</t>
@@ -111,10 +120,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -126,12 +135,103 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -139,8 +239,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -154,58 +255,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -214,56 +263,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,187 +287,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -472,11 +481,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -498,26 +513,18 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -563,9 +570,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -577,145 +586,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1156,7 +1165,7 @@
         <v>12</v>
       </c>
       <c r="D5">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1170,7 +1179,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D6">
         <v>0.8</v>
@@ -1184,10 +1193,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D7">
         <v>0.8</v>
@@ -1201,10 +1210,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1218,10 +1227,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1235,10 +1244,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D10">
         <v>0.8</v>
@@ -1252,10 +1261,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D11">
         <v>0.6</v>
@@ -1269,10 +1278,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D12">
         <v>0.8</v>
@@ -1286,10 +1295,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1303,10 +1312,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D14">
         <v>0.6</v>
@@ -1320,10 +1329,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D15">
         <v>0.8</v>
@@ -1337,10 +1346,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D16">
         <v>0.8</v>
@@ -1354,10 +1363,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D17">
         <v>0.8</v>
@@ -1371,16 +1380,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D18">
         <v>0.8</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1388,10 +1397,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D19">
         <v>0.8</v>
@@ -1405,7 +1414,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
@@ -1422,7 +1431,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C21" t="s">
         <v>6</v>

--- a/Assets/Data/SE.xlsx
+++ b/Assets/Data/SE.xlsx
@@ -120,10 +120,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -134,30 +134,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -171,77 +165,38 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -255,26 +210,71 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -287,13 +287,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -305,43 +389,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -353,25 +431,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -383,79 +455,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -478,21 +478,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -515,25 +500,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -549,6 +516,21 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -570,6 +552,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -578,6 +569,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -586,145 +586,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/SE.xlsx
+++ b/Assets/Data/SE.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
   <si>
     <t>Id</t>
   </si>
@@ -34,85 +34,115 @@
     <t>DECIDE</t>
   </si>
   <si>
-    <t>cursor33</t>
+    <t>decide7</t>
   </si>
   <si>
     <t>CANCEL</t>
   </si>
   <si>
-    <t>cursor27</t>
-  </si>
-  <si>
     <t>CURSOR</t>
   </si>
   <si>
-    <t>cursor11</t>
+    <t>cursor_move8</t>
   </si>
   <si>
     <t>DAMAGE</t>
   </si>
   <si>
-    <t>Damage4</t>
+    <t>damage</t>
   </si>
   <si>
     <t>DEFEAT</t>
   </si>
   <si>
-    <t>Collapse1</t>
+    <t>defeat</t>
   </si>
   <si>
     <t>DEMIGOD</t>
   </si>
   <si>
-    <t>cursor32</t>
+    <t>swordspecial</t>
   </si>
   <si>
     <t>DENY</t>
   </si>
   <si>
-    <t>Shot2</t>
+    <t>beap3</t>
   </si>
   <si>
     <t>LEVELUP</t>
   </si>
   <si>
+    <t>decide43</t>
+  </si>
+  <si>
     <t>CRITICAL</t>
   </si>
   <si>
+    <t>Sword2</t>
+  </si>
+  <si>
     <t>SKILL</t>
   </si>
   <si>
+    <t>Skill1</t>
+  </si>
+  <si>
     <t>AWAKEN</t>
   </si>
   <si>
+    <t>demigod</t>
+  </si>
+  <si>
     <t>COUNTUP</t>
   </si>
   <si>
+    <t>messagedisplay1</t>
+  </si>
+  <si>
     <t>MISS</t>
   </si>
   <si>
+    <t>Miss</t>
+  </si>
+  <si>
     <t>HEAL</t>
   </si>
   <si>
+    <t>Up1</t>
+  </si>
+  <si>
     <t>BUFF</t>
   </si>
   <si>
+    <t>Sword1</t>
+  </si>
+  <si>
     <t>DEBUFF</t>
   </si>
   <si>
+    <t>power36</t>
+  </si>
+  <si>
     <t>BATTLESTART</t>
   </si>
   <si>
-    <t>Battle3</t>
-  </si>
-  <si>
     <t>LEARNSKILL</t>
   </si>
   <si>
+    <t>Flash2</t>
+  </si>
+  <si>
     <t>CURSOR_MOVE</t>
   </si>
   <si>
+    <t>cursor</t>
+  </si>
+  <si>
     <t>PLAYSTART</t>
+  </si>
+  <si>
+    <t>gamestart</t>
   </si>
 </sst>
 </file>
@@ -120,10 +150,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -131,29 +161,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -165,6 +172,80 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -173,30 +254,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -210,71 +278,33 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -287,19 +317,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -311,37 +377,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -353,115 +485,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -478,21 +508,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -520,17 +535,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -550,11 +574,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -569,15 +608,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -586,145 +616,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1128,7 +1158,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1142,10 +1172,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
         <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1159,13 +1189,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
       <c r="D5">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1176,10 +1206,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
       </c>
       <c r="D6">
         <v>0.8</v>
@@ -1193,10 +1223,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
         <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
       </c>
       <c r="D7">
         <v>0.8</v>
@@ -1210,10 +1240,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
         <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1227,10 +1257,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
         <v>19</v>
-      </c>
-      <c r="C9" t="s">
-        <v>16</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1247,10 +1277,10 @@
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D10">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1261,13 +1291,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D11">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1278,13 +1308,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D12">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1295,10 +1325,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1312,13 +1342,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D14">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1329,13 +1359,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D15">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1346,13 +1376,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D16">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -1363,13 +1393,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="D17">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -1380,13 +1410,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D18">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E18">
         <v>0.7</v>
@@ -1397,13 +1427,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D19">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1414,13 +1444,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D20">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -1431,13 +1461,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="D21">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E21">
         <v>1</v>
